--- a/files/Cases/SodaVendingMachine/RQ3_SodaVendingMachine_perProduct_rawData.xlsx
+++ b/files/Cases/SodaVendingMachine/RQ3_SodaVendingMachine_perProduct_rawData.xlsx
@@ -421,6 +421,24 @@
   </sheetPr>
   <dimension ref="A1:P97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="39" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -522,7 +540,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EFG_L2</t>
+          <t>ESG-Fx_L1</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -535,16 +553,16 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
         <v>4.5</v>
       </c>
       <c r="J2" t="n">
-        <v>16.67</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>16.67</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="L2" t="n">
         <v>6</v>
@@ -582,7 +600,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EFG_L3</t>
+          <t>ESG-Fx_L2</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -595,16 +613,16 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
         <v>4.5</v>
       </c>
       <c r="J3" t="n">
-        <v>18</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>18</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="L3" t="n">
         <v>6</v>
@@ -642,7 +660,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EFG_L4</t>
+          <t>ESG-Fx_L3</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -655,16 +673,16 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
         <v>4.5</v>
       </c>
       <c r="J4" t="n">
-        <v>20.45</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>20.45</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="L4" t="n">
         <v>6</v>
@@ -702,7 +720,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ESG-Fx_L0</t>
+          <t>ESG-Fx_L4</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -762,7 +780,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ESG-Fx_L1</t>
+          <t>EFG_L2</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -775,16 +793,16 @@
         <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="I6" t="n">
         <v>4.5</v>
       </c>
       <c r="J6" t="n">
-        <v>64.29000000000001</v>
+        <v>16.67</v>
       </c>
       <c r="K6" t="n">
-        <v>64.29000000000001</v>
+        <v>16.67</v>
       </c>
       <c r="L6" t="n">
         <v>6</v>
@@ -822,7 +840,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ESG-Fx_L2</t>
+          <t>EFG_L3</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -835,16 +853,16 @@
         <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="I7" t="n">
         <v>4.5</v>
       </c>
       <c r="J7" t="n">
-        <v>64.29000000000001</v>
+        <v>18</v>
       </c>
       <c r="K7" t="n">
-        <v>64.29000000000001</v>
+        <v>18</v>
       </c>
       <c r="L7" t="n">
         <v>6</v>
@@ -882,7 +900,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ESG-Fx_L3</t>
+          <t>EFG_L4</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -895,16 +913,16 @@
         <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="I8" t="n">
         <v>4.5</v>
       </c>
       <c r="J8" t="n">
-        <v>64.29000000000001</v>
+        <v>20.45</v>
       </c>
       <c r="K8" t="n">
-        <v>64.29000000000001</v>
+        <v>20.45</v>
       </c>
       <c r="L8" t="n">
         <v>6</v>
@@ -942,7 +960,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ESG-Fx_L4</t>
+          <t>RandomWalk</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1002,7 +1020,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EFG_L2</t>
+          <t>ESG-Fx_L1</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1015,16 +1033,16 @@
         <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
         <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>33.33</v>
+        <v>75</v>
       </c>
       <c r="K10" t="n">
-        <v>33.33</v>
+        <v>75</v>
       </c>
       <c r="L10" t="n">
         <v>3</v>
@@ -1062,7 +1080,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EFG_L3</t>
+          <t>ESG-Fx_L2</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1075,16 +1093,16 @@
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
         <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>42.86</v>
+        <v>75</v>
       </c>
       <c r="K11" t="n">
-        <v>42.86</v>
+        <v>75</v>
       </c>
       <c r="L11" t="n">
         <v>3</v>
@@ -1122,7 +1140,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EFG_L4</t>
+          <t>ESG-Fx_L3</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1182,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ESG-Fx_L0</t>
+          <t>ESG-Fx_L4</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1242,7 +1260,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ESG-Fx_L1</t>
+          <t>EFG_L2</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1255,16 +1273,16 @@
         <v>100</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I14" t="n">
         <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>75</v>
+        <v>33.33</v>
       </c>
       <c r="K14" t="n">
-        <v>75</v>
+        <v>33.33</v>
       </c>
       <c r="L14" t="n">
         <v>3</v>
@@ -1302,7 +1320,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ESG-Fx_L2</t>
+          <t>EFG_L3</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1315,16 +1333,16 @@
         <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I15" t="n">
         <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>75</v>
+        <v>42.86</v>
       </c>
       <c r="K15" t="n">
-        <v>75</v>
+        <v>42.86</v>
       </c>
       <c r="L15" t="n">
         <v>3</v>
@@ -1362,7 +1380,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ESG-Fx_L3</t>
+          <t>EFG_L4</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1422,7 +1440,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ESG-Fx_L4</t>
+          <t>RandomWalk</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1482,7 +1500,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EFG_L2</t>
+          <t>ESG-Fx_L1</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1495,16 +1513,16 @@
         <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="I18" t="n">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="J18" t="n">
-        <v>30.88</v>
+        <v>50</v>
       </c>
       <c r="K18" t="n">
-        <v>30.88</v>
+        <v>50</v>
       </c>
       <c r="L18" t="n">
         <v>8</v>
@@ -1542,7 +1560,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EFG_L3</t>
+          <t>ESG-Fx_L2</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1555,16 +1573,16 @@
         <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="I19" t="n">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="J19" t="n">
-        <v>32.81</v>
+        <v>50</v>
       </c>
       <c r="K19" t="n">
-        <v>32.81</v>
+        <v>50</v>
       </c>
       <c r="L19" t="n">
         <v>8</v>
@@ -1602,7 +1620,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EFG_L4</t>
+          <t>ESG-Fx_L3</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1615,16 +1633,16 @@
         <v>100</v>
       </c>
       <c r="H20" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="I20" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="J20" t="n">
-        <v>28.85</v>
+        <v>50</v>
       </c>
       <c r="K20" t="n">
-        <v>28.85</v>
+        <v>50</v>
       </c>
       <c r="L20" t="n">
         <v>8</v>
@@ -1662,7 +1680,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ESG-Fx_L0</t>
+          <t>ESG-Fx_L4</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1678,13 +1696,13 @@
         <v>11</v>
       </c>
       <c r="I21" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="J21" t="n">
-        <v>68.18000000000001</v>
+        <v>50</v>
       </c>
       <c r="K21" t="n">
-        <v>68.18000000000001</v>
+        <v>50</v>
       </c>
       <c r="L21" t="n">
         <v>8</v>
@@ -1722,7 +1740,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ESG-Fx_L1</t>
+          <t>EFG_L2</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1735,16 +1753,16 @@
         <v>100</v>
       </c>
       <c r="H22" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="I22" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="J22" t="n">
-        <v>50</v>
+        <v>30.88</v>
       </c>
       <c r="K22" t="n">
-        <v>50</v>
+        <v>30.88</v>
       </c>
       <c r="L22" t="n">
         <v>8</v>
@@ -1782,7 +1800,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ESG-Fx_L2</t>
+          <t>EFG_L3</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1795,16 +1813,16 @@
         <v>100</v>
       </c>
       <c r="H23" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="I23" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="J23" t="n">
-        <v>50</v>
+        <v>32.81</v>
       </c>
       <c r="K23" t="n">
-        <v>50</v>
+        <v>32.81</v>
       </c>
       <c r="L23" t="n">
         <v>8</v>
@@ -1842,7 +1860,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ESG-Fx_L3</t>
+          <t>EFG_L4</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1855,16 +1873,16 @@
         <v>100</v>
       </c>
       <c r="H24" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="I24" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="J24" t="n">
-        <v>50</v>
+        <v>28.85</v>
       </c>
       <c r="K24" t="n">
-        <v>50</v>
+        <v>28.85</v>
       </c>
       <c r="L24" t="n">
         <v>8</v>
@@ -1902,7 +1920,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ESG-Fx_L4</t>
+          <t>RandomWalk</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1918,13 +1936,13 @@
         <v>11</v>
       </c>
       <c r="I25" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="J25" t="n">
-        <v>50</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>50</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="L25" t="n">
         <v>8</v>
@@ -1962,7 +1980,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EFG_L2</t>
+          <t>ESG-Fx_L1</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1975,16 +1993,16 @@
         <v>100</v>
       </c>
       <c r="H26" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J26" t="n">
-        <v>35.71</v>
+        <v>57.14</v>
       </c>
       <c r="K26" t="n">
-        <v>35.71</v>
+        <v>57.14</v>
       </c>
       <c r="L26" t="n">
         <v>5</v>
@@ -2022,7 +2040,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EFG_L3</t>
+          <t>ESG-Fx_L2</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -2035,16 +2053,16 @@
         <v>100</v>
       </c>
       <c r="H27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
-        <v>70</v>
+        <v>57.14</v>
       </c>
       <c r="K27" t="n">
-        <v>70</v>
+        <v>57.14</v>
       </c>
       <c r="L27" t="n">
         <v>5</v>
@@ -2082,7 +2100,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EFG_L4</t>
+          <t>ESG-Fx_L3</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -2142,7 +2160,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ESG-Fx_L0</t>
+          <t>ESG-Fx_L4</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -2158,13 +2176,13 @@
         <v>7</v>
       </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
-        <v>71.43000000000001</v>
+        <v>57.14</v>
       </c>
       <c r="K29" t="n">
-        <v>71.43000000000001</v>
+        <v>57.14</v>
       </c>
       <c r="L29" t="n">
         <v>5</v>
@@ -2202,7 +2220,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ESG-Fx_L1</t>
+          <t>EFG_L2</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -2215,16 +2233,16 @@
         <v>100</v>
       </c>
       <c r="H30" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30" t="n">
-        <v>57.14</v>
+        <v>35.71</v>
       </c>
       <c r="K30" t="n">
-        <v>57.14</v>
+        <v>35.71</v>
       </c>
       <c r="L30" t="n">
         <v>5</v>
@@ -2262,7 +2280,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ESG-Fx_L2</t>
+          <t>EFG_L3</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -2275,16 +2293,16 @@
         <v>100</v>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J31" t="n">
-        <v>57.14</v>
+        <v>70</v>
       </c>
       <c r="K31" t="n">
-        <v>57.14</v>
+        <v>70</v>
       </c>
       <c r="L31" t="n">
         <v>5</v>
@@ -2322,7 +2340,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ESG-Fx_L3</t>
+          <t>EFG_L4</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -2382,7 +2400,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ESG-Fx_L4</t>
+          <t>RandomWalk</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -2398,13 +2416,13 @@
         <v>7</v>
       </c>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J33" t="n">
-        <v>57.14</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>57.14</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="L33" t="n">
         <v>5</v>
@@ -2442,7 +2460,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>EFG_L2</t>
+          <t>ESG-Fx_L1</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -2455,16 +2473,16 @@
         <v>100</v>
       </c>
       <c r="H34" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="I34" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="J34" t="n">
-        <v>27.78</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>27.78</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="L34" t="n">
         <v>6</v>
@@ -2502,7 +2520,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>EFG_L3</t>
+          <t>ESG-Fx_L2</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -2515,16 +2533,16 @@
         <v>100</v>
       </c>
       <c r="H35" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="I35" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="J35" t="n">
-        <v>30</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>30</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="L35" t="n">
         <v>6</v>
@@ -2562,7 +2580,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EFG_L4</t>
+          <t>ESG-Fx_L3</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -2575,16 +2593,16 @@
         <v>100</v>
       </c>
       <c r="H36" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="I36" t="n">
         <v>4.5</v>
       </c>
       <c r="J36" t="n">
-        <v>20.45</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>20.45</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="L36" t="n">
         <v>6</v>
@@ -2622,7 +2640,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ESG-Fx_L0</t>
+          <t>ESG-Fx_L4</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -2682,7 +2700,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ESG-Fx_L1</t>
+          <t>EFG_L2</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -2695,16 +2713,16 @@
         <v>100</v>
       </c>
       <c r="H38" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="I38" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="J38" t="n">
-        <v>64.29000000000001</v>
+        <v>27.78</v>
       </c>
       <c r="K38" t="n">
-        <v>64.29000000000001</v>
+        <v>27.78</v>
       </c>
       <c r="L38" t="n">
         <v>6</v>
@@ -2742,7 +2760,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ESG-Fx_L2</t>
+          <t>EFG_L3</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -2755,16 +2773,16 @@
         <v>100</v>
       </c>
       <c r="H39" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="I39" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="J39" t="n">
-        <v>64.29000000000001</v>
+        <v>30</v>
       </c>
       <c r="K39" t="n">
-        <v>64.29000000000001</v>
+        <v>30</v>
       </c>
       <c r="L39" t="n">
         <v>6</v>
@@ -2802,7 +2820,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ESG-Fx_L3</t>
+          <t>EFG_L4</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -2815,16 +2833,16 @@
         <v>100</v>
       </c>
       <c r="H40" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="I40" t="n">
         <v>4.5</v>
       </c>
       <c r="J40" t="n">
-        <v>64.29000000000001</v>
+        <v>20.45</v>
       </c>
       <c r="K40" t="n">
-        <v>64.29000000000001</v>
+        <v>20.45</v>
       </c>
       <c r="L40" t="n">
         <v>6</v>
@@ -2862,7 +2880,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ESG-Fx_L4</t>
+          <t>RandomWalk</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -2922,7 +2940,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>EFG_L2</t>
+          <t>ESG-Fx_L1</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -2935,16 +2953,16 @@
         <v>100</v>
       </c>
       <c r="H42" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I42" t="n">
         <v>3</v>
       </c>
       <c r="J42" t="n">
-        <v>33.33</v>
+        <v>75</v>
       </c>
       <c r="K42" t="n">
-        <v>33.33</v>
+        <v>75</v>
       </c>
       <c r="L42" t="n">
         <v>3</v>
@@ -2982,7 +3000,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EFG_L3</t>
+          <t>ESG-Fx_L2</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -2995,16 +3013,16 @@
         <v>100</v>
       </c>
       <c r="H43" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I43" t="n">
         <v>3</v>
       </c>
       <c r="J43" t="n">
-        <v>42.86</v>
+        <v>75</v>
       </c>
       <c r="K43" t="n">
-        <v>42.86</v>
+        <v>75</v>
       </c>
       <c r="L43" t="n">
         <v>3</v>
@@ -3042,7 +3060,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>EFG_L4</t>
+          <t>ESG-Fx_L3</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -3102,7 +3120,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ESG-Fx_L0</t>
+          <t>ESG-Fx_L4</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -3162,7 +3180,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ESG-Fx_L1</t>
+          <t>EFG_L2</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -3175,16 +3193,16 @@
         <v>100</v>
       </c>
       <c r="H46" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I46" t="n">
         <v>3</v>
       </c>
       <c r="J46" t="n">
-        <v>75</v>
+        <v>33.33</v>
       </c>
       <c r="K46" t="n">
-        <v>75</v>
+        <v>33.33</v>
       </c>
       <c r="L46" t="n">
         <v>3</v>
@@ -3222,7 +3240,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ESG-Fx_L2</t>
+          <t>EFG_L3</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -3235,16 +3253,16 @@
         <v>100</v>
       </c>
       <c r="H47" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I47" t="n">
         <v>3</v>
       </c>
       <c r="J47" t="n">
-        <v>75</v>
+        <v>42.86</v>
       </c>
       <c r="K47" t="n">
-        <v>75</v>
+        <v>42.86</v>
       </c>
       <c r="L47" t="n">
         <v>3</v>
@@ -3282,7 +3300,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ESG-Fx_L3</t>
+          <t>EFG_L4</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -3342,7 +3360,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ESG-Fx_L4</t>
+          <t>RandomWalk</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -3402,7 +3420,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>EFG_L2</t>
+          <t>ESG-Fx_L1</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -3415,16 +3433,16 @@
         <v>100</v>
       </c>
       <c r="H50" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="I50" t="n">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="J50" t="n">
-        <v>30.88</v>
+        <v>50</v>
       </c>
       <c r="K50" t="n">
-        <v>30.88</v>
+        <v>50</v>
       </c>
       <c r="L50" t="n">
         <v>8</v>
@@ -3462,7 +3480,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>EFG_L3</t>
+          <t>ESG-Fx_L2</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -3475,16 +3493,16 @@
         <v>100</v>
       </c>
       <c r="H51" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="I51" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="J51" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="K51" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="L51" t="n">
         <v>8</v>
@@ -3522,7 +3540,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>EFG_L4</t>
+          <t>ESG-Fx_L3</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -3535,16 +3553,16 @@
         <v>100</v>
       </c>
       <c r="H52" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="I52" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="J52" t="n">
-        <v>28.85</v>
+        <v>50</v>
       </c>
       <c r="K52" t="n">
-        <v>28.85</v>
+        <v>50</v>
       </c>
       <c r="L52" t="n">
         <v>8</v>
@@ -3582,7 +3600,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ESG-Fx_L0</t>
+          <t>ESG-Fx_L4</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -3598,13 +3616,13 @@
         <v>11</v>
       </c>
       <c r="I53" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="J53" t="n">
-        <v>68.18000000000001</v>
+        <v>50</v>
       </c>
       <c r="K53" t="n">
-        <v>68.18000000000001</v>
+        <v>50</v>
       </c>
       <c r="L53" t="n">
         <v>8</v>
@@ -3642,7 +3660,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ESG-Fx_L1</t>
+          <t>EFG_L2</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -3655,16 +3673,16 @@
         <v>100</v>
       </c>
       <c r="H54" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="I54" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="J54" t="n">
-        <v>50</v>
+        <v>30.88</v>
       </c>
       <c r="K54" t="n">
-        <v>50</v>
+        <v>30.88</v>
       </c>
       <c r="L54" t="n">
         <v>8</v>
@@ -3702,7 +3720,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ESG-Fx_L2</t>
+          <t>EFG_L3</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -3715,16 +3733,16 @@
         <v>100</v>
       </c>
       <c r="H55" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="I55" t="n">
-        <v>5.5</v>
+        <v>12</v>
       </c>
       <c r="J55" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="K55" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="L55" t="n">
         <v>8</v>
@@ -3762,7 +3780,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ESG-Fx_L3</t>
+          <t>EFG_L4</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -3775,16 +3793,16 @@
         <v>100</v>
       </c>
       <c r="H56" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="I56" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="J56" t="n">
-        <v>50</v>
+        <v>28.85</v>
       </c>
       <c r="K56" t="n">
-        <v>50</v>
+        <v>28.85</v>
       </c>
       <c r="L56" t="n">
         <v>8</v>
@@ -3822,7 +3840,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ESG-Fx_L4</t>
+          <t>RandomWalk</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -3838,13 +3856,13 @@
         <v>11</v>
       </c>
       <c r="I57" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="J57" t="n">
-        <v>50</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>50</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="L57" t="n">
         <v>8</v>
@@ -3882,7 +3900,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>EFG_L2</t>
+          <t>ESG-Fx_L1</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -3895,16 +3913,16 @@
         <v>100</v>
       </c>
       <c r="H58" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J58" t="n">
-        <v>35.71</v>
+        <v>57.14</v>
       </c>
       <c r="K58" t="n">
-        <v>35.71</v>
+        <v>57.14</v>
       </c>
       <c r="L58" t="n">
         <v>5</v>
@@ -3942,7 +3960,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>EFG_L3</t>
+          <t>ESG-Fx_L2</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -3955,16 +3973,16 @@
         <v>100</v>
       </c>
       <c r="H59" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I59" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J59" t="n">
-        <v>70</v>
+        <v>57.14</v>
       </c>
       <c r="K59" t="n">
-        <v>70</v>
+        <v>57.14</v>
       </c>
       <c r="L59" t="n">
         <v>5</v>
@@ -4002,7 +4020,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>EFG_L4</t>
+          <t>ESG-Fx_L3</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -4062,7 +4080,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ESG-Fx_L0</t>
+          <t>ESG-Fx_L4</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -4122,7 +4140,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ESG-Fx_L1</t>
+          <t>EFG_L2</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -4135,16 +4153,16 @@
         <v>100</v>
       </c>
       <c r="H62" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J62" t="n">
-        <v>57.14</v>
+        <v>35.71</v>
       </c>
       <c r="K62" t="n">
-        <v>57.14</v>
+        <v>35.71</v>
       </c>
       <c r="L62" t="n">
         <v>5</v>
@@ -4182,7 +4200,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ESG-Fx_L2</t>
+          <t>EFG_L3</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -4195,16 +4213,16 @@
         <v>100</v>
       </c>
       <c r="H63" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I63" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J63" t="n">
-        <v>57.14</v>
+        <v>70</v>
       </c>
       <c r="K63" t="n">
-        <v>57.14</v>
+        <v>70</v>
       </c>
       <c r="L63" t="n">
         <v>5</v>
@@ -4242,7 +4260,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ESG-Fx_L3</t>
+          <t>EFG_L4</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -4302,7 +4320,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ESG-Fx_L4</t>
+          <t>RandomWalk</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -4362,7 +4380,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>EFG_L2</t>
+          <t>ESG-Fx_L1</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -4375,16 +4393,16 @@
         <v>100</v>
       </c>
       <c r="H66" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="I66" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J66" t="n">
-        <v>32.61</v>
+        <v>38.89</v>
       </c>
       <c r="K66" t="n">
-        <v>32.61</v>
+        <v>38.89</v>
       </c>
       <c r="L66" t="n">
         <v>11</v>
@@ -4422,7 +4440,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>EFG_L3</t>
+          <t>ESG-Fx_L2</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -4435,16 +4453,16 @@
         <v>100</v>
       </c>
       <c r="H67" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="I67" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J67" t="n">
-        <v>30</v>
+        <v>38.89</v>
       </c>
       <c r="K67" t="n">
-        <v>30</v>
+        <v>38.89</v>
       </c>
       <c r="L67" t="n">
         <v>11</v>
@@ -4482,7 +4500,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EFG_L4</t>
+          <t>ESG-Fx_L3</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -4495,16 +4513,16 @@
         <v>100</v>
       </c>
       <c r="H68" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="I68" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J68" t="n">
-        <v>18.75</v>
+        <v>38.89</v>
       </c>
       <c r="K68" t="n">
-        <v>18.75</v>
+        <v>38.89</v>
       </c>
       <c r="L68" t="n">
         <v>11</v>
@@ -4542,7 +4560,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ESG-Fx_L0</t>
+          <t>ESG-Fx_L4</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -4558,13 +4576,13 @@
         <v>18</v>
       </c>
       <c r="I69" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J69" t="n">
-        <v>50</v>
+        <v>38.89</v>
       </c>
       <c r="K69" t="n">
-        <v>50</v>
+        <v>38.89</v>
       </c>
       <c r="L69" t="n">
         <v>11</v>
@@ -4602,7 +4620,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ESG-Fx_L1</t>
+          <t>EFG_L2</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -4615,16 +4633,16 @@
         <v>100</v>
       </c>
       <c r="H70" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="I70" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J70" t="n">
-        <v>38.89</v>
+        <v>32.61</v>
       </c>
       <c r="K70" t="n">
-        <v>38.89</v>
+        <v>32.61</v>
       </c>
       <c r="L70" t="n">
         <v>11</v>
@@ -4662,7 +4680,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ESG-Fx_L2</t>
+          <t>EFG_L3</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -4675,16 +4693,16 @@
         <v>100</v>
       </c>
       <c r="H71" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="I71" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J71" t="n">
-        <v>38.89</v>
+        <v>30</v>
       </c>
       <c r="K71" t="n">
-        <v>38.89</v>
+        <v>30</v>
       </c>
       <c r="L71" t="n">
         <v>11</v>
@@ -4722,7 +4740,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ESG-Fx_L3</t>
+          <t>EFG_L4</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -4735,16 +4753,16 @@
         <v>100</v>
       </c>
       <c r="H72" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="I72" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J72" t="n">
-        <v>38.89</v>
+        <v>18.75</v>
       </c>
       <c r="K72" t="n">
-        <v>38.89</v>
+        <v>18.75</v>
       </c>
       <c r="L72" t="n">
         <v>11</v>
@@ -4782,7 +4800,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ESG-Fx_L4</t>
+          <t>RandomWalk</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -4798,13 +4816,13 @@
         <v>18</v>
       </c>
       <c r="I73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J73" t="n">
-        <v>38.89</v>
+        <v>50</v>
       </c>
       <c r="K73" t="n">
-        <v>38.89</v>
+        <v>50</v>
       </c>
       <c r="L73" t="n">
         <v>11</v>
@@ -4842,7 +4860,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>EFG_L2</t>
+          <t>ESG-Fx_L1</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -4855,16 +4873,16 @@
         <v>100</v>
       </c>
       <c r="H74" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="I74" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J74" t="n">
-        <v>20.51</v>
+        <v>42.86</v>
       </c>
       <c r="K74" t="n">
-        <v>20.51</v>
+        <v>42.86</v>
       </c>
       <c r="L74" t="n">
         <v>9</v>
@@ -4902,7 +4920,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>EFG_L3</t>
+          <t>ESG-Fx_L2</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -4915,16 +4933,16 @@
         <v>100</v>
       </c>
       <c r="H75" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="I75" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J75" t="n">
-        <v>18.6</v>
+        <v>42.86</v>
       </c>
       <c r="K75" t="n">
-        <v>18.6</v>
+        <v>42.86</v>
       </c>
       <c r="L75" t="n">
         <v>9</v>
@@ -4962,7 +4980,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>EFG_L4</t>
+          <t>ESG-Fx_L3</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -4975,16 +4993,16 @@
         <v>100</v>
       </c>
       <c r="H76" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="I76" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J76" t="n">
-        <v>18.18</v>
+        <v>42.86</v>
       </c>
       <c r="K76" t="n">
-        <v>18.18</v>
+        <v>42.86</v>
       </c>
       <c r="L76" t="n">
         <v>9</v>
@@ -5022,7 +5040,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ESG-Fx_L0</t>
+          <t>ESG-Fx_L4</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -5082,7 +5100,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ESG-Fx_L1</t>
+          <t>EFG_L2</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -5095,16 +5113,16 @@
         <v>100</v>
       </c>
       <c r="H78" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="I78" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J78" t="n">
-        <v>42.86</v>
+        <v>20.51</v>
       </c>
       <c r="K78" t="n">
-        <v>42.86</v>
+        <v>20.51</v>
       </c>
       <c r="L78" t="n">
         <v>9</v>
@@ -5142,7 +5160,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ESG-Fx_L2</t>
+          <t>EFG_L3</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -5155,16 +5173,16 @@
         <v>100</v>
       </c>
       <c r="H79" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="I79" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J79" t="n">
-        <v>42.86</v>
+        <v>18.6</v>
       </c>
       <c r="K79" t="n">
-        <v>42.86</v>
+        <v>18.6</v>
       </c>
       <c r="L79" t="n">
         <v>9</v>
@@ -5202,7 +5220,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ESG-Fx_L3</t>
+          <t>EFG_L4</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -5215,16 +5233,16 @@
         <v>100</v>
       </c>
       <c r="H80" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="I80" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J80" t="n">
-        <v>42.86</v>
+        <v>18.18</v>
       </c>
       <c r="K80" t="n">
-        <v>42.86</v>
+        <v>18.18</v>
       </c>
       <c r="L80" t="n">
         <v>9</v>
@@ -5262,7 +5280,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ESG-Fx_L4</t>
+          <t>RandomWalk</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -5322,7 +5340,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>EFG_L2</t>
+          <t>ESG-Fx_L1</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -5335,16 +5353,16 @@
         <v>100</v>
       </c>
       <c r="H82" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I82" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J82" t="n">
-        <v>30.56</v>
+        <v>62.5</v>
       </c>
       <c r="K82" t="n">
-        <v>30.56</v>
+        <v>62.5</v>
       </c>
       <c r="L82" t="n">
         <v>6</v>
@@ -5382,7 +5400,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>EFG_L3</t>
+          <t>ESG-Fx_L2</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -5395,16 +5413,16 @@
         <v>100</v>
       </c>
       <c r="H83" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I83" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J83" t="n">
-        <v>39.29</v>
+        <v>62.5</v>
       </c>
       <c r="K83" t="n">
-        <v>39.29</v>
+        <v>62.5</v>
       </c>
       <c r="L83" t="n">
         <v>6</v>
@@ -5442,7 +5460,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EFG_L4</t>
+          <t>ESG-Fx_L3</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -5502,7 +5520,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ESG-Fx_L0</t>
+          <t>ESG-Fx_L4</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -5562,7 +5580,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ESG-Fx_L1</t>
+          <t>EFG_L2</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -5575,16 +5593,16 @@
         <v>100</v>
       </c>
       <c r="H86" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I86" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="J86" t="n">
-        <v>62.5</v>
+        <v>30.56</v>
       </c>
       <c r="K86" t="n">
-        <v>62.5</v>
+        <v>30.56</v>
       </c>
       <c r="L86" t="n">
         <v>6</v>
@@ -5622,7 +5640,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ESG-Fx_L2</t>
+          <t>EFG_L3</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -5635,16 +5653,16 @@
         <v>100</v>
       </c>
       <c r="H87" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I87" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="J87" t="n">
-        <v>62.5</v>
+        <v>39.29</v>
       </c>
       <c r="K87" t="n">
-        <v>62.5</v>
+        <v>39.29</v>
       </c>
       <c r="L87" t="n">
         <v>6</v>
@@ -5682,7 +5700,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ESG-Fx_L3</t>
+          <t>EFG_L4</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -5742,7 +5760,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ESG-Fx_L4</t>
+          <t>RandomWalk</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -5802,7 +5820,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>EFG_L2</t>
+          <t>ESG-Fx_L1</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -5815,16 +5833,16 @@
         <v>100</v>
       </c>
       <c r="H90" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="I90" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="J90" t="n">
-        <v>32.61</v>
+        <v>59.09</v>
       </c>
       <c r="K90" t="n">
-        <v>32.61</v>
+        <v>59.09</v>
       </c>
       <c r="L90" t="n">
         <v>8</v>
@@ -5862,7 +5880,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>EFG_L3</t>
+          <t>ESG-Fx_L2</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -5875,16 +5893,16 @@
         <v>100</v>
       </c>
       <c r="H91" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I91" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="J91" t="n">
-        <v>47.06</v>
+        <v>59.09</v>
       </c>
       <c r="K91" t="n">
-        <v>47.06</v>
+        <v>59.09</v>
       </c>
       <c r="L91" t="n">
         <v>8</v>
@@ -5922,7 +5940,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>EFG_L4</t>
+          <t>ESG-Fx_L3</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -5982,7 +6000,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ESG-Fx_L0</t>
+          <t>ESG-Fx_L4</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -6042,7 +6060,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ESG-Fx_L1</t>
+          <t>EFG_L2</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -6055,16 +6073,16 @@
         <v>100</v>
       </c>
       <c r="H94" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="I94" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="J94" t="n">
-        <v>59.09</v>
+        <v>32.61</v>
       </c>
       <c r="K94" t="n">
-        <v>59.09</v>
+        <v>32.61</v>
       </c>
       <c r="L94" t="n">
         <v>8</v>
@@ -6102,7 +6120,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ESG-Fx_L2</t>
+          <t>EFG_L3</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -6115,16 +6133,16 @@
         <v>100</v>
       </c>
       <c r="H95" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I95" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="J95" t="n">
-        <v>59.09</v>
+        <v>47.06</v>
       </c>
       <c r="K95" t="n">
-        <v>59.09</v>
+        <v>47.06</v>
       </c>
       <c r="L95" t="n">
         <v>8</v>
@@ -6162,7 +6180,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ESG-Fx_L3</t>
+          <t>EFG_L4</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -6222,7 +6240,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ESG-Fx_L4</t>
+          <t>RandomWalk</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -6277,6 +6295,24 @@
   </sheetPr>
   <dimension ref="A1:P97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="39" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -6378,7 +6414,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EFG_L2</t>
+          <t>ESG-Fx_L1</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -6391,16 +6427,16 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>14.81</v>
+        <v>57.14</v>
       </c>
       <c r="K2" t="n">
-        <v>14.81</v>
+        <v>57.14</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -6438,7 +6474,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EFG_L3</t>
+          <t>ESG-Fx_L2</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -6451,16 +6487,16 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>16</v>
+        <v>57.14</v>
       </c>
       <c r="K3" t="n">
-        <v>16</v>
+        <v>57.14</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -6498,7 +6534,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EFG_L4</t>
+          <t>ESG-Fx_L3</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -6511,16 +6547,16 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
         <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>18.18</v>
+        <v>57.14</v>
       </c>
       <c r="K4" t="n">
-        <v>18.18</v>
+        <v>57.14</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -6558,7 +6594,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ESG-Fx_L0</t>
+          <t>ESG-Fx_L4</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -6618,7 +6654,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ESG-Fx_L1</t>
+          <t>EFG_L2</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -6631,16 +6667,16 @@
         <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="I6" t="n">
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>57.14</v>
+        <v>14.81</v>
       </c>
       <c r="K6" t="n">
-        <v>57.14</v>
+        <v>14.81</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -6678,7 +6714,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ESG-Fx_L2</t>
+          <t>EFG_L3</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -6691,16 +6727,16 @@
         <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="I7" t="n">
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>57.14</v>
+        <v>16</v>
       </c>
       <c r="K7" t="n">
-        <v>57.14</v>
+        <v>16</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -6738,7 +6774,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ESG-Fx_L3</t>
+          <t>EFG_L4</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -6751,16 +6787,16 @@
         <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="I8" t="n">
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>57.14</v>
+        <v>18.18</v>
       </c>
       <c r="K8" t="n">
-        <v>57.14</v>
+        <v>18.18</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -6798,7 +6834,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ESG-Fx_L4</t>
+          <t>RandomWalk</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -6858,7 +6894,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EFG_L2</t>
+          <t>ESG-Fx_L1</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -6871,16 +6907,16 @@
         <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
         <v>2.5</v>
       </c>
       <c r="J10" t="n">
-        <v>27.78</v>
+        <v>62.5</v>
       </c>
       <c r="K10" t="n">
-        <v>27.78</v>
+        <v>62.5</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -6918,7 +6954,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EFG_L3</t>
+          <t>ESG-Fx_L2</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -6931,16 +6967,16 @@
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
         <v>2.5</v>
       </c>
       <c r="J11" t="n">
-        <v>35.71</v>
+        <v>62.5</v>
       </c>
       <c r="K11" t="n">
-        <v>35.71</v>
+        <v>62.5</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6978,7 +7014,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EFG_L4</t>
+          <t>ESG-Fx_L3</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -7038,7 +7074,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ESG-Fx_L0</t>
+          <t>ESG-Fx_L4</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -7098,7 +7134,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ESG-Fx_L1</t>
+          <t>EFG_L2</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -7111,16 +7147,16 @@
         <v>100</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I14" t="n">
         <v>2.5</v>
       </c>
       <c r="J14" t="n">
-        <v>62.5</v>
+        <v>27.78</v>
       </c>
       <c r="K14" t="n">
-        <v>62.5</v>
+        <v>27.78</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -7158,7 +7194,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ESG-Fx_L2</t>
+          <t>EFG_L3</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -7171,16 +7207,16 @@
         <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I15" t="n">
         <v>2.5</v>
       </c>
       <c r="J15" t="n">
-        <v>62.5</v>
+        <v>35.71</v>
       </c>
       <c r="K15" t="n">
-        <v>62.5</v>
+        <v>35.71</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -7218,7 +7254,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ESG-Fx_L3</t>
+          <t>EFG_L4</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -7278,7 +7314,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ESG-Fx_L4</t>
+          <t>RandomWalk</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -7338,7 +7374,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EFG_L2</t>
+          <t>ESG-Fx_L1</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -7351,16 +7387,16 @@
         <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="I18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>29.41</v>
+        <v>45.45</v>
       </c>
       <c r="K18" t="n">
-        <v>29.41</v>
+        <v>45.45</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -7398,7 +7434,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EFG_L3</t>
+          <t>ESG-Fx_L2</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -7411,16 +7447,16 @@
         <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="I19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
-        <v>31.25</v>
+        <v>45.45</v>
       </c>
       <c r="K19" t="n">
-        <v>31.25</v>
+        <v>45.45</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -7458,7 +7494,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EFG_L4</t>
+          <t>ESG-Fx_L3</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -7471,16 +7507,16 @@
         <v>100</v>
       </c>
       <c r="H20" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="I20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>26.92</v>
+        <v>45.45</v>
       </c>
       <c r="K20" t="n">
-        <v>26.92</v>
+        <v>45.45</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -7518,7 +7554,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ESG-Fx_L0</t>
+          <t>ESG-Fx_L4</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -7534,13 +7570,13 @@
         <v>11</v>
       </c>
       <c r="I21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J21" t="n">
-        <v>63.64</v>
+        <v>45.45</v>
       </c>
       <c r="K21" t="n">
-        <v>63.64</v>
+        <v>45.45</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -7578,7 +7614,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ESG-Fx_L1</t>
+          <t>EFG_L2</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -7591,16 +7627,16 @@
         <v>100</v>
       </c>
       <c r="H22" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>45.45</v>
+        <v>29.41</v>
       </c>
       <c r="K22" t="n">
-        <v>45.45</v>
+        <v>29.41</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -7638,7 +7674,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ESG-Fx_L2</t>
+          <t>EFG_L3</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -7651,16 +7687,16 @@
         <v>100</v>
       </c>
       <c r="H23" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>45.45</v>
+        <v>31.25</v>
       </c>
       <c r="K23" t="n">
-        <v>45.45</v>
+        <v>31.25</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -7698,7 +7734,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ESG-Fx_L3</t>
+          <t>EFG_L4</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -7711,16 +7747,16 @@
         <v>100</v>
       </c>
       <c r="H24" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J24" t="n">
-        <v>45.45</v>
+        <v>26.92</v>
       </c>
       <c r="K24" t="n">
-        <v>45.45</v>
+        <v>26.92</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -7758,7 +7794,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ESG-Fx_L4</t>
+          <t>RandomWalk</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -7774,13 +7810,13 @@
         <v>11</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J25" t="n">
-        <v>45.45</v>
+        <v>63.64</v>
       </c>
       <c r="K25" t="n">
-        <v>45.45</v>
+        <v>63.64</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -7818,7 +7854,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EFG_L2</t>
+          <t>ESG-Fx_L1</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -7831,16 +7867,16 @@
         <v>100</v>
       </c>
       <c r="H26" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I26" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="J26" t="n">
-        <v>32.14</v>
+        <v>50</v>
       </c>
       <c r="K26" t="n">
-        <v>32.14</v>
+        <v>50</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -7878,7 +7914,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EFG_L3</t>
+          <t>ESG-Fx_L2</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -7891,10 +7927,10 @@
         <v>100</v>
       </c>
       <c r="H27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="J27" t="n">
         <v>50</v>
@@ -7938,7 +7974,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EFG_L4</t>
+          <t>ESG-Fx_L3</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -7998,7 +8034,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ESG-Fx_L0</t>
+          <t>ESG-Fx_L4</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -8014,13 +8050,13 @@
         <v>7</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="J29" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="K29" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -8058,7 +8094,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ESG-Fx_L1</t>
+          <t>EFG_L2</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -8071,16 +8107,16 @@
         <v>100</v>
       </c>
       <c r="H30" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I30" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="J30" t="n">
-        <v>50</v>
+        <v>32.14</v>
       </c>
       <c r="K30" t="n">
-        <v>50</v>
+        <v>32.14</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -8118,7 +8154,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ESG-Fx_L2</t>
+          <t>EFG_L3</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -8131,10 +8167,10 @@
         <v>100</v>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I31" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="J31" t="n">
         <v>50</v>
@@ -8178,7 +8214,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ESG-Fx_L3</t>
+          <t>EFG_L4</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -8238,7 +8274,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ESG-Fx_L4</t>
+          <t>RandomWalk</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -8254,13 +8290,13 @@
         <v>7</v>
       </c>
       <c r="I33" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J33" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="K33" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -8298,7 +8334,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>EFG_L2</t>
+          <t>ESG-Fx_L1</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -8311,16 +8347,16 @@
         <v>100</v>
       </c>
       <c r="H34" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="I34" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J34" t="n">
-        <v>25.93</v>
+        <v>57.14</v>
       </c>
       <c r="K34" t="n">
-        <v>25.93</v>
+        <v>57.14</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -8358,7 +8394,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>EFG_L3</t>
+          <t>ESG-Fx_L2</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -8371,16 +8407,16 @@
         <v>100</v>
       </c>
       <c r="H35" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="I35" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
-        <v>28</v>
+        <v>57.14</v>
       </c>
       <c r="K35" t="n">
-        <v>28</v>
+        <v>57.14</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -8418,7 +8454,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EFG_L4</t>
+          <t>ESG-Fx_L3</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -8431,16 +8467,16 @@
         <v>100</v>
       </c>
       <c r="H36" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="I36" t="n">
         <v>4</v>
       </c>
       <c r="J36" t="n">
-        <v>18.18</v>
+        <v>57.14</v>
       </c>
       <c r="K36" t="n">
-        <v>18.18</v>
+        <v>57.14</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -8478,7 +8514,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ESG-Fx_L0</t>
+          <t>ESG-Fx_L4</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -8538,7 +8574,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ESG-Fx_L1</t>
+          <t>EFG_L2</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -8551,16 +8587,16 @@
         <v>100</v>
       </c>
       <c r="H38" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J38" t="n">
-        <v>57.14</v>
+        <v>25.93</v>
       </c>
       <c r="K38" t="n">
-        <v>57.14</v>
+        <v>25.93</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -8598,7 +8634,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ESG-Fx_L2</t>
+          <t>EFG_L3</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -8611,16 +8647,16 @@
         <v>100</v>
       </c>
       <c r="H39" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J39" t="n">
-        <v>57.14</v>
+        <v>28</v>
       </c>
       <c r="K39" t="n">
-        <v>57.14</v>
+        <v>28</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -8658,7 +8694,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ESG-Fx_L3</t>
+          <t>EFG_L4</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -8671,16 +8707,16 @@
         <v>100</v>
       </c>
       <c r="H40" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="I40" t="n">
         <v>4</v>
       </c>
       <c r="J40" t="n">
-        <v>57.14</v>
+        <v>18.18</v>
       </c>
       <c r="K40" t="n">
-        <v>57.14</v>
+        <v>18.18</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -8718,7 +8754,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ESG-Fx_L4</t>
+          <t>RandomWalk</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -8778,7 +8814,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>EFG_L2</t>
+          <t>ESG-Fx_L1</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -8791,16 +8827,16 @@
         <v>100</v>
       </c>
       <c r="H42" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I42" t="n">
         <v>2.5</v>
       </c>
       <c r="J42" t="n">
-        <v>27.78</v>
+        <v>62.5</v>
       </c>
       <c r="K42" t="n">
-        <v>27.78</v>
+        <v>62.5</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -8838,7 +8874,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EFG_L3</t>
+          <t>ESG-Fx_L2</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -8851,16 +8887,16 @@
         <v>100</v>
       </c>
       <c r="H43" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I43" t="n">
         <v>2.5</v>
       </c>
       <c r="J43" t="n">
-        <v>35.71</v>
+        <v>62.5</v>
       </c>
       <c r="K43" t="n">
-        <v>35.71</v>
+        <v>62.5</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -8898,7 +8934,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>EFG_L4</t>
+          <t>ESG-Fx_L3</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -8958,7 +8994,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ESG-Fx_L0</t>
+          <t>ESG-Fx_L4</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -9018,7 +9054,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ESG-Fx_L1</t>
+          <t>EFG_L2</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -9031,16 +9067,16 @@
         <v>100</v>
       </c>
       <c r="H46" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I46" t="n">
         <v>2.5</v>
       </c>
       <c r="J46" t="n">
-        <v>62.5</v>
+        <v>27.78</v>
       </c>
       <c r="K46" t="n">
-        <v>62.5</v>
+        <v>27.78</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -9078,7 +9114,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ESG-Fx_L2</t>
+          <t>EFG_L3</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -9091,16 +9127,16 @@
         <v>100</v>
       </c>
       <c r="H47" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I47" t="n">
         <v>2.5</v>
       </c>
       <c r="J47" t="n">
-        <v>62.5</v>
+        <v>35.71</v>
       </c>
       <c r="K47" t="n">
-        <v>62.5</v>
+        <v>35.71</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -9138,7 +9174,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ESG-Fx_L3</t>
+          <t>EFG_L4</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -9198,7 +9234,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ESG-Fx_L4</t>
+          <t>RandomWalk</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -9258,7 +9294,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>EFG_L2</t>
+          <t>ESG-Fx_L1</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -9271,16 +9307,16 @@
         <v>100</v>
       </c>
       <c r="H50" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="I50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J50" t="n">
-        <v>29.41</v>
+        <v>45.45</v>
       </c>
       <c r="K50" t="n">
-        <v>29.41</v>
+        <v>45.45</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -9318,7 +9354,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>EFG_L3</t>
+          <t>ESG-Fx_L2</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -9331,16 +9367,16 @@
         <v>100</v>
       </c>
       <c r="H51" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="I51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J51" t="n">
-        <v>31.25</v>
+        <v>45.45</v>
       </c>
       <c r="K51" t="n">
-        <v>31.25</v>
+        <v>45.45</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -9378,7 +9414,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>EFG_L4</t>
+          <t>ESG-Fx_L3</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -9391,16 +9427,16 @@
         <v>100</v>
       </c>
       <c r="H52" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="I52" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J52" t="n">
-        <v>26.92</v>
+        <v>45.45</v>
       </c>
       <c r="K52" t="n">
-        <v>26.92</v>
+        <v>45.45</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -9438,7 +9474,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ESG-Fx_L0</t>
+          <t>ESG-Fx_L4</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -9454,13 +9490,13 @@
         <v>11</v>
       </c>
       <c r="I53" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J53" t="n">
-        <v>63.64</v>
+        <v>45.45</v>
       </c>
       <c r="K53" t="n">
-        <v>63.64</v>
+        <v>45.45</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -9498,7 +9534,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ESG-Fx_L1</t>
+          <t>EFG_L2</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -9511,16 +9547,16 @@
         <v>100</v>
       </c>
       <c r="H54" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="I54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J54" t="n">
-        <v>45.45</v>
+        <v>29.41</v>
       </c>
       <c r="K54" t="n">
-        <v>45.45</v>
+        <v>29.41</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -9558,7 +9594,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ESG-Fx_L2</t>
+          <t>EFG_L3</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -9571,16 +9607,16 @@
         <v>100</v>
       </c>
       <c r="H55" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="I55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>45.45</v>
+        <v>31.25</v>
       </c>
       <c r="K55" t="n">
-        <v>45.45</v>
+        <v>31.25</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -9618,7 +9654,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ESG-Fx_L3</t>
+          <t>EFG_L4</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -9631,16 +9667,16 @@
         <v>100</v>
       </c>
       <c r="H56" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="I56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J56" t="n">
-        <v>45.45</v>
+        <v>26.92</v>
       </c>
       <c r="K56" t="n">
-        <v>45.45</v>
+        <v>26.92</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -9678,7 +9714,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ESG-Fx_L4</t>
+          <t>RandomWalk</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -9694,13 +9730,13 @@
         <v>11</v>
       </c>
       <c r="I57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J57" t="n">
-        <v>45.45</v>
+        <v>63.64</v>
       </c>
       <c r="K57" t="n">
-        <v>45.45</v>
+        <v>63.64</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -9738,7 +9774,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>EFG_L2</t>
+          <t>ESG-Fx_L1</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -9751,16 +9787,16 @@
         <v>100</v>
       </c>
       <c r="H58" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I58" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="J58" t="n">
-        <v>32.14</v>
+        <v>50</v>
       </c>
       <c r="K58" t="n">
-        <v>32.14</v>
+        <v>50</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -9798,7 +9834,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>EFG_L3</t>
+          <t>ESG-Fx_L2</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -9811,10 +9847,10 @@
         <v>100</v>
       </c>
       <c r="H59" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="J59" t="n">
         <v>50</v>
@@ -9858,7 +9894,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>EFG_L4</t>
+          <t>ESG-Fx_L3</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -9918,7 +9954,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ESG-Fx_L0</t>
+          <t>ESG-Fx_L4</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -9978,7 +10014,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ESG-Fx_L1</t>
+          <t>EFG_L2</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -9991,16 +10027,16 @@
         <v>100</v>
       </c>
       <c r="H62" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I62" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="J62" t="n">
-        <v>50</v>
+        <v>32.14</v>
       </c>
       <c r="K62" t="n">
-        <v>50</v>
+        <v>32.14</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -10038,7 +10074,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ESG-Fx_L2</t>
+          <t>EFG_L3</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -10051,10 +10087,10 @@
         <v>100</v>
       </c>
       <c r="H63" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I63" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="J63" t="n">
         <v>50</v>
@@ -10098,7 +10134,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ESG-Fx_L3</t>
+          <t>EFG_L4</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -10158,7 +10194,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ESG-Fx_L4</t>
+          <t>RandomWalk</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -10218,7 +10254,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>EFG_L2</t>
+          <t>ESG-Fx_L1</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -10231,16 +10267,16 @@
         <v>100</v>
       </c>
       <c r="H66" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="I66" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J66" t="n">
-        <v>30.43</v>
+        <v>33.33</v>
       </c>
       <c r="K66" t="n">
-        <v>30.43</v>
+        <v>33.33</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -10278,7 +10314,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>EFG_L3</t>
+          <t>ESG-Fx_L2</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -10291,16 +10327,16 @@
         <v>100</v>
       </c>
       <c r="H67" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="I67" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J67" t="n">
-        <v>28</v>
+        <v>33.33</v>
       </c>
       <c r="K67" t="n">
-        <v>28</v>
+        <v>33.33</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -10338,7 +10374,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EFG_L4</t>
+          <t>ESG-Fx_L3</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -10351,16 +10387,16 @@
         <v>100</v>
       </c>
       <c r="H68" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="I68" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J68" t="n">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="K68" t="n">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -10398,7 +10434,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ESG-Fx_L0</t>
+          <t>ESG-Fx_L4</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -10414,13 +10450,13 @@
         <v>18</v>
       </c>
       <c r="I69" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J69" t="n">
-        <v>44.44</v>
+        <v>33.33</v>
       </c>
       <c r="K69" t="n">
-        <v>44.44</v>
+        <v>33.33</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -10458,7 +10494,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ESG-Fx_L1</t>
+          <t>EFG_L2</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -10471,16 +10507,16 @@
         <v>100</v>
       </c>
       <c r="H70" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="I70" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J70" t="n">
-        <v>33.33</v>
+        <v>30.43</v>
       </c>
       <c r="K70" t="n">
-        <v>33.33</v>
+        <v>30.43</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -10518,7 +10554,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ESG-Fx_L2</t>
+          <t>EFG_L3</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -10531,16 +10567,16 @@
         <v>100</v>
       </c>
       <c r="H71" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="I71" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J71" t="n">
-        <v>33.33</v>
+        <v>28</v>
       </c>
       <c r="K71" t="n">
-        <v>33.33</v>
+        <v>28</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -10578,7 +10614,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ESG-Fx_L3</t>
+          <t>EFG_L4</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -10591,16 +10627,16 @@
         <v>100</v>
       </c>
       <c r="H72" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="I72" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J72" t="n">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="K72" t="n">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -10638,7 +10674,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ESG-Fx_L4</t>
+          <t>RandomWalk</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -10654,13 +10690,13 @@
         <v>18</v>
       </c>
       <c r="I73" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J73" t="n">
-        <v>33.33</v>
+        <v>44.44</v>
       </c>
       <c r="K73" t="n">
-        <v>33.33</v>
+        <v>44.44</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -10698,7 +10734,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>EFG_L2</t>
+          <t>ESG-Fx_L1</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -10711,16 +10747,16 @@
         <v>100</v>
       </c>
       <c r="H74" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="I74" t="n">
         <v>5</v>
       </c>
       <c r="J74" t="n">
-        <v>12.82</v>
+        <v>35.71</v>
       </c>
       <c r="K74" t="n">
-        <v>12.82</v>
+        <v>35.71</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -10758,7 +10794,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>EFG_L3</t>
+          <t>ESG-Fx_L2</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -10771,16 +10807,16 @@
         <v>100</v>
       </c>
       <c r="H75" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="I75" t="n">
         <v>5</v>
       </c>
       <c r="J75" t="n">
-        <v>11.63</v>
+        <v>35.71</v>
       </c>
       <c r="K75" t="n">
-        <v>11.63</v>
+        <v>35.71</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -10818,7 +10854,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>EFG_L4</t>
+          <t>ESG-Fx_L3</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -10831,16 +10867,16 @@
         <v>100</v>
       </c>
       <c r="H76" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="I76" t="n">
         <v>5</v>
       </c>
       <c r="J76" t="n">
-        <v>11.36</v>
+        <v>35.71</v>
       </c>
       <c r="K76" t="n">
-        <v>11.36</v>
+        <v>35.71</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -10878,7 +10914,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ESG-Fx_L0</t>
+          <t>ESG-Fx_L4</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -10938,7 +10974,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ESG-Fx_L1</t>
+          <t>EFG_L2</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -10951,16 +10987,16 @@
         <v>100</v>
       </c>
       <c r="H78" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="I78" t="n">
         <v>5</v>
       </c>
       <c r="J78" t="n">
-        <v>35.71</v>
+        <v>12.82</v>
       </c>
       <c r="K78" t="n">
-        <v>35.71</v>
+        <v>12.82</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -10998,7 +11034,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ESG-Fx_L2</t>
+          <t>EFG_L3</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -11011,16 +11047,16 @@
         <v>100</v>
       </c>
       <c r="H79" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="I79" t="n">
         <v>5</v>
       </c>
       <c r="J79" t="n">
-        <v>35.71</v>
+        <v>11.63</v>
       </c>
       <c r="K79" t="n">
-        <v>35.71</v>
+        <v>11.63</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -11058,7 +11094,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ESG-Fx_L3</t>
+          <t>EFG_L4</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -11071,16 +11107,16 @@
         <v>100</v>
       </c>
       <c r="H80" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="I80" t="n">
         <v>5</v>
       </c>
       <c r="J80" t="n">
-        <v>35.71</v>
+        <v>11.36</v>
       </c>
       <c r="K80" t="n">
-        <v>35.71</v>
+        <v>11.36</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -11118,7 +11154,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ESG-Fx_L4</t>
+          <t>RandomWalk</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -11178,7 +11214,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>EFG_L2</t>
+          <t>ESG-Fx_L1</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -11191,16 +11227,16 @@
         <v>100</v>
       </c>
       <c r="H82" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I82" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="J82" t="n">
-        <v>22.22</v>
+        <v>43.75</v>
       </c>
       <c r="K82" t="n">
-        <v>22.22</v>
+        <v>43.75</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -11238,7 +11274,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>EFG_L3</t>
+          <t>ESG-Fx_L2</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -11251,16 +11287,16 @@
         <v>100</v>
       </c>
       <c r="H83" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I83" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="J83" t="n">
-        <v>28.57</v>
+        <v>43.75</v>
       </c>
       <c r="K83" t="n">
-        <v>28.57</v>
+        <v>43.75</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -11298,7 +11334,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EFG_L4</t>
+          <t>ESG-Fx_L3</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -11358,7 +11394,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ESG-Fx_L0</t>
+          <t>ESG-Fx_L4</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -11418,7 +11454,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ESG-Fx_L1</t>
+          <t>EFG_L2</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -11431,16 +11467,16 @@
         <v>100</v>
       </c>
       <c r="H86" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I86" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J86" t="n">
-        <v>43.75</v>
+        <v>22.22</v>
       </c>
       <c r="K86" t="n">
-        <v>43.75</v>
+        <v>22.22</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -11478,7 +11514,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ESG-Fx_L2</t>
+          <t>EFG_L3</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -11491,16 +11527,16 @@
         <v>100</v>
       </c>
       <c r="H87" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I87" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J87" t="n">
-        <v>43.75</v>
+        <v>28.57</v>
       </c>
       <c r="K87" t="n">
-        <v>43.75</v>
+        <v>28.57</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -11538,7 +11574,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ESG-Fx_L3</t>
+          <t>EFG_L4</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -11598,7 +11634,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ESG-Fx_L4</t>
+          <t>RandomWalk</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -11658,7 +11694,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>EFG_L2</t>
+          <t>ESG-Fx_L1</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -11671,16 +11707,16 @@
         <v>100</v>
       </c>
       <c r="H90" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="I90" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J90" t="n">
-        <v>26.09</v>
+        <v>45.45</v>
       </c>
       <c r="K90" t="n">
-        <v>26.09</v>
+        <v>45.45</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -11718,7 +11754,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>EFG_L3</t>
+          <t>ESG-Fx_L2</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -11731,16 +11767,16 @@
         <v>100</v>
       </c>
       <c r="H91" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I91" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J91" t="n">
-        <v>32.35</v>
+        <v>45.45</v>
       </c>
       <c r="K91" t="n">
-        <v>32.35</v>
+        <v>45.45</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -11778,7 +11814,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>EFG_L4</t>
+          <t>ESG-Fx_L3</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -11838,7 +11874,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ESG-Fx_L0</t>
+          <t>ESG-Fx_L4</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -11898,7 +11934,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ESG-Fx_L1</t>
+          <t>EFG_L2</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -11911,16 +11947,16 @@
         <v>100</v>
       </c>
       <c r="H94" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="I94" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J94" t="n">
-        <v>45.45</v>
+        <v>26.09</v>
       </c>
       <c r="K94" t="n">
-        <v>45.45</v>
+        <v>26.09</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -11958,7 +11994,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ESG-Fx_L2</t>
+          <t>EFG_L3</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -11971,16 +12007,16 @@
         <v>100</v>
       </c>
       <c r="H95" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I95" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="J95" t="n">
-        <v>45.45</v>
+        <v>32.35</v>
       </c>
       <c r="K95" t="n">
-        <v>45.45</v>
+        <v>32.35</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -12018,7 +12054,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ESG-Fx_L3</t>
+          <t>EFG_L4</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -12078,7 +12114,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ESG-Fx_L4</t>
+          <t>RandomWalk</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -12133,6 +12169,24 @@
   </sheetPr>
   <dimension ref="A1:P121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -19189,6 +19243,24 @@
   </sheetPr>
   <dimension ref="A1:P121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -26245,6 +26317,24 @@
   </sheetPr>
   <dimension ref="A1:P37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -28501,6 +28591,24 @@
   </sheetPr>
   <dimension ref="A1:P37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -30757,6 +30865,16 @@
   </sheetPr>
   <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
